--- a/bnc-streamlit-app/data/points/6zhd6pt8kyzrbkgwq2i2k8u1g_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/6zhd6pt8kyzrbkgwq2i2k8u1g_playerlog.xlsx
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -955,14 +955,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -1008,21 +1008,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1587343</v>
+        <v>-0.11569904</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1142,14 +1142,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1195,30 +1195,30 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>0.12968152</v>
+        <v>0.94467989</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1325,14 +1325,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.22725346</v>
+        <v>0.30097492</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>+0.09</t>
+          <t>+0.11</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1565,11 +1565,11 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.28876565</v>
+        <v>0.63536079</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.44</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1597,10 +1597,10 @@
         <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="BE6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1699,14 +1699,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>0.14985989</v>
+        <v>0.26103138</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>+0.01</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="BE7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1886,14 +1886,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1939,21 +1939,21 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>0.03867826000000001</v>
+        <v>0.13105376</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>
@@ -2069,14 +2069,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2122,21 +2122,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.15360126</v>
+        <v>0.25693374</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>+0.02</t>
+          <t>+0.06</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2256,14 +2256,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.8739235299999999</v>
+        <v>0.6680151</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>+0.74</t>
+          <t>+0.47</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2443,14 +2443,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>0.2232297</v>
+        <v>1.11324512</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>+0.09</t>
+          <t>+0.92</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2525,7 +2525,7 @@
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         </is>
       </c>
       <c r="BE11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG11" t="n">
         <v>2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2630,14 +2630,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>0.10882551</v>
+        <v>0.36856311</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>+0.17</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -2813,14 +2813,14 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2984,14 +2984,14 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -3023,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG14" t="n">
         <v>1</v>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.3808046199999999</v>
+        <v>-0.1066331500000001</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -3167,14 +3167,14 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>0.12972356</v>
+        <v>-0.04713017000000002</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3350,14 +3350,14 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>0.04112503000000002</v>
+        <v>-0.14525429</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3533,14 +3533,14 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG17" t="n">
         <v>1</v>
@@ -3586,21 +3586,21 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>0.07933372999999999</v>
+        <v>-0.08749384000000002</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3716,14 +3716,14 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG18" t="n">
         <v>1</v>
@@ -3769,21 +3769,21 @@
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>0.41495335</v>
+        <v>0.2354502</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>+0.28</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -3810,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3899,14 +3899,14 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>0.0143409</v>
+        <v>0.0240099</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -4082,14 +4082,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG20" t="n">
         <v>1</v>
@@ -4135,21 +4135,21 @@
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>0.02778284000000002</v>
+        <v>0.06570752000000001</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
         <v>1</v>
@@ -4265,14 +4265,14 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>-0.03267428000000001</v>
+        <v>-0.008937310000000018</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -4448,14 +4448,14 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG22" t="n">
         <v>1</v>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.0868236</v>
+        <v>0.02256683999999998</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -4631,14 +4631,14 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -4684,21 +4684,21 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>-0.02712260000000002</v>
+        <v>-0.02745209000000001</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>3</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>

--- a/bnc-streamlit-app/data/points/6zhd6pt8kyzrbkgwq2i2k8u1g_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/6zhd6pt8kyzrbkgwq2i2k8u1g_playerlog.xlsx
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -955,14 +955,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1142,14 +1142,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>0.94467989</v>
+        <v>0.87919087</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.69</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1325,14 +1325,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.30097492</v>
+        <v>0.31574571</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>+0.13</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1565,11 +1565,11 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.63536079</v>
+        <v>0.637059</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>+0.44</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1699,14 +1699,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>0.26103138</v>
+        <v>0.21581043</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>+0.07</t>
+          <t>+0.03</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1886,14 +1886,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -2069,14 +2069,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2122,21 +2122,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.25693374</v>
+        <v>0.27815503</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>+0.06</t>
+          <t>+0.09</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS9" t="n">
         <v>1</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2256,14 +2256,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2309,11 +2309,11 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.6680151</v>
+        <v>0.66646281</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>+0.47</t>
+          <t>+0.48</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2443,14 +2443,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>1.11324512</v>
+        <v>1.11494333</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>+0.92</t>
+          <t>+0.93</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2630,14 +2630,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>0.36856311</v>
+        <v>0.27916567</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>+0.17</t>
+          <t>+0.09</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2813,14 +2813,14 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2984,14 +2984,14 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3167,14 +3167,14 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3220,11 +3220,11 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>-0.04713017000000002</v>
+        <v>-0.04797557000000002</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3350,14 +3350,14 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3403,11 +3403,11 @@
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>-0.14525429</v>
+        <v>-0.13725429</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3533,14 +3533,14 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>-0.08749384000000002</v>
+        <v>-0.09789004000000004</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3716,14 +3716,14 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3773,17 +3773,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -3899,14 +3899,14 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3956,17 +3956,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -4082,14 +4082,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -4265,14 +4265,14 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -4448,14 +4448,14 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.02256683999999998</v>
+        <v>0.02561540000000001</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>1</v>
@@ -4631,14 +4631,14 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4684,11 +4684,11 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>-0.02745209000000001</v>
+        <v>-0.02846852000000002</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>

--- a/bnc-streamlit-app/data/points/6zhd6pt8kyzrbkgwq2i2k8u1g_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/6zhd6pt8kyzrbkgwq2i2k8u1g_playerlog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG23"/>
+  <dimension ref="A1:BG33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
@@ -955,14 +955,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="AG3" t="n">
         <v>1</v>
@@ -1008,21 +1008,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>-0.11569904</v>
+        <v>0.72573725</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>+0.34</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1034,16 +1034,16 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="n">
         <v>2</v>
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1128,10 +1128,12 @@
           <t>br7zigajqee6fms35zhm1sb8p</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1142,14 +1144,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1157,7 +1159,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1184,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1195,21 +1197,21 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>0.87919087</v>
+        <v>0.74295269</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>+0.69</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1224,17 +1226,17 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
         <v>3</v>
       </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
@@ -1242,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -1325,14 +1327,18 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>42</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1340,10 +1346,16 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>42</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1361,13 +1373,13 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1378,21 +1390,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.31574571</v>
+        <v>0.57870825</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>+0.13</t>
+          <t>+0.19</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1407,54 +1419,54 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
         <v>1</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="BE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1498,10 +1510,12 @@
           <t>2w7i4jfw5wgh3j2wuworoumeh</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1512,14 +1526,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1527,7 +1541,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1557,7 +1571,7 @@
         <v>-0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1565,21 +1579,21 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.637059</v>
+        <v>1.03624068</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.65</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1597,10 +1611,10 @@
         <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
@@ -1635,7 +1649,7 @@
         </is>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1699,14 +1713,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1714,7 +1728,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1735,13 +1749,13 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
@@ -1752,21 +1766,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>0.21581043</v>
+        <v>1.01952806</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>+0.03</t>
+          <t>+0.63</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1775,22 +1789,22 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -1822,13 +1836,13 @@
         </is>
       </c>
       <c r="BE7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1872,10 +1886,12 @@
           <t>3ga7qj3h3dbmqucxmaxhmrjdh</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1886,14 +1902,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1901,7 +1917,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1928,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1939,21 +1955,21 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>0.13105376</v>
+        <v>0.42851286</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -1968,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>
@@ -2069,14 +2085,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2084,7 +2100,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2105,13 +2121,13 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
         <v>1</v>
@@ -2122,42 +2138,42 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.27815503</v>
+        <v>0.86555929</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>+0.09</t>
+          <t>+0.48</t>
         </is>
       </c>
       <c r="AK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
         <v>7</v>
       </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3</v>
-      </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
         <v>2</v>
@@ -2192,13 +2208,13 @@
         </is>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2242,10 +2258,12 @@
           <t>7r2tgpdrr4v6n9d2gkzwmlazt</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -2256,14 +2274,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2271,7 +2289,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2301,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2309,21 +2327,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.66646281</v>
+        <v>0.4724985299999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>+0.48</t>
+          <t>+0.08</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2335,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>3</v>
@@ -2347,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -2379,13 +2397,13 @@
         </is>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2443,14 +2461,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2458,7 +2476,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2479,7 +2497,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -2496,11 +2514,11 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>1.11494333</v>
+        <v>2.36644753</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>+0.93</t>
+          <t>+1.98</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -2510,22 +2528,22 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -2534,13 +2552,13 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2566,13 +2584,13 @@
         </is>
       </c>
       <c r="BE11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2616,10 +2634,12 @@
           <t>4ea0sjczqa5ah1w720zlakkfe</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -2630,14 +2650,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2645,7 +2665,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2672,10 +2692,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2683,21 +2703,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>0.27916567</v>
+        <v>0.43560593</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>+0.09</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2706,22 +2726,22 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -2752,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2766,37 +2786,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Schlager</t>
+          <t>N. Tagliafico</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> 3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8btyl5lum9zndjh1rxuzdfowl</t>
+          <t>40hu79d2a4k94nc52z7dblpsl</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2805,30 +2825,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>81</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2840,35 +2864,47 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>N. Tagliafico</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.25411043</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>19</v>
+      </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AM13" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2886,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
@@ -2895,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2918,15 +2954,19 @@
       <c r="BC13" t="n">
         <v>0</v>
       </c>
-      <c r="BD13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2937,12 +2977,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S. Posch</t>
+          <t>L. Paredes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2952,22 +2992,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1po7tmdv73zfjentt0p20wdlh</t>
+          <t>apdtqouzo9b02ozdxk8mx4zbp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2976,33 +3016,47 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>81</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>42</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>RCM(2)</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>42</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>RCM(2)</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -3011,47 +3065,47 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2</v>
+        <v>-0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>S. Posch</t>
+          <t>L. Paredes</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>-0.1066331500000001</v>
+        <v>-0.24888781</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AM14" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3060,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3069,13 +3123,13 @@
         <v>1</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -3106,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3120,37 +3174,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K. Laimer</t>
+          <t>J. Alvarez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 20</t>
+          <t xml:space="preserve"> 9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1qthvf5krys0pzk24h8wtr9at</t>
+          <t>9ikkuxd19avliz1khcrm82gyy</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3159,30 +3213,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>63</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3194,47 +3252,47 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>K. Laimer</t>
+          <t>J. Alvarez</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>-0.04797557000000002</v>
+        <v>0.37512471</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AM15" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3246,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
@@ -3264,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
@@ -3284,15 +3342,19 @@
       <c r="BC15" t="n">
         <v>0</v>
       </c>
-      <c r="BD15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF15" t="n">
         <v>1</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3303,37 +3365,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>X. Schlager</t>
+          <t>N. González</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4</t>
+          <t xml:space="preserve"> 15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LCM(2)</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1s1v1tweyx8wxc9hj2jrnaggl</t>
+          <t>eh1ul4duphy1iz4odwx9tkjjd</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -3342,30 +3404,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>64</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>LCM(2)</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3377,47 +3443,47 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05</v>
+        <v>-0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>X. Schlager</t>
+          <t>N. González</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>-0.13725429</v>
+        <v>0.9024328099999999</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>+0.51</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AM16" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3429,13 +3495,13 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
@@ -3472,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3486,17 +3552,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K. Danso</t>
+          <t>N. Otamendi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3</t>
+          <t xml:space="preserve"> 19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3506,17 +3572,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4ezld812zytvbokz97jwycgkp</t>
+          <t>x32fbvwwxkda9ruezw67b3dh</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3525,22 +3591,26 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>56</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q17" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3548,7 +3618,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3560,47 +3630,47 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>61g4epojd5f198lv1sje27yh3</t>
+          <t>ak48fkypnql8y4n69cvcq5ghc</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.2</v>
+        <v>-0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>K. Danso</t>
+          <t>N. Otamendi</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>-0.09789004000000004</v>
+        <v>0.13434545</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AM17" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3612,16 +3682,16 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
@@ -3655,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3674,17 +3744,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>D. Alaba</t>
+          <t>A. Schlager</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LCB(2)</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3694,12 +3764,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6w5wyari2p4bh2zzy2x2f6hg5</t>
+          <t>8btyl5lum9zndjh1rxuzdfowl</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3716,22 +3786,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>LCB(2)</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3755,35 +3825,23 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>1</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>D. Alaba</t>
-        </is>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.2354502</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>8</v>
-      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -3795,22 +3853,22 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3838,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3857,17 +3915,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R. Schmid</t>
+          <t>S. Posch</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18</t>
+          <t xml:space="preserve"> 5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3877,18 +3935,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>b4q9q0qgmtz959rygieg9ln1l</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>1po7tmdv73zfjentt0p20wdlh</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -3899,22 +3959,22 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3941,32 +4001,32 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>R. Schmid</t>
+          <t>S. Posch</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>0.0240099</v>
+        <v>-0.1620839400000001</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3975,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -3990,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -3999,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -4021,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4040,17 +4100,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N. Seiwald</t>
+          <t>K. Laimer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6</t>
+          <t xml:space="preserve"> 20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RCM(2)</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4060,12 +4120,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>307whzq643o50rd4g8niobyay</t>
+          <t>1qthvf5krys0pzk24h8wtr9at</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -4082,25 +4142,35 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>42</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>RCM(2)</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>42</v>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+        <v>67.3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>29.7</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -4121,35 +4191,35 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="AG20" t="n">
         <v>1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>N. Seiwald</t>
+          <t>K. Laimer</t>
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>0.06570752000000001</v>
+        <v>-0.19027034</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -4161,16 +4231,16 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS20" t="n">
         <v>1</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="n">
         <v>1</v>
@@ -4182,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -4204,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4223,17 +4293,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M. Gregoritsch</t>
+          <t>X. Schlager</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11</t>
+          <t xml:space="preserve"> 4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LCM(2)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4243,12 +4313,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7c6034wb3zsuq9nhxxiahiuol</t>
+          <t>1s1v1tweyx8wxc9hj2jrnaggl</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -4265,22 +4335,22 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LCM(2)</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4304,35 +4374,35 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AG21" t="n">
         <v>1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>M. Gregoritsch</t>
+          <t>X. Schlager</t>
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>-0.008937310000000018</v>
+        <v>0.13600573</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -4347,16 +4417,16 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -4406,17 +4476,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P. Wanner</t>
+          <t>K. Danso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 24</t>
+          <t xml:space="preserve"> 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RCB(2)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4426,12 +4496,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2yc1t7u26zctwjizi283g6q6s</t>
+          <t>4ezld812zytvbokz97jwycgkp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4448,22 +4518,22 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RCB(2)</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4487,35 +4557,35 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="AG22" t="n">
         <v>1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>P. Wanner</t>
+          <t>K. Danso</t>
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.02561540000000001</v>
+        <v>0.2513859899999999</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -4527,22 +4597,22 @@
         <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>1</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -4570,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4589,17 +4659,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M. Sabitzer</t>
+          <t>D. Alaba</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9</t>
+          <t xml:space="preserve"> 8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>LCB(2)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4609,18 +4679,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8cho2d1nz18i5o0zt6aysd68l</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6w5wyari2p4bh2zzy2x2f6hg5</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -4631,22 +4703,22 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>LCB(2)</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4673,32 +4745,32 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>M. Sabitzer</t>
+          <t>D. Alaba</t>
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>-0.02846852000000002</v>
+        <v>0.70499173</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>+0.32</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -4710,14 +4782,14 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
         <v>3</v>
       </c>
-      <c r="AR23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
       <c r="AT23" t="n">
         <v>1</v>
       </c>
@@ -4725,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW23" t="n">
         <v>0</v>
@@ -4753,9 +4825,1885 @@
         <v>0</v>
       </c>
       <c r="BF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R. Schmid</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>b4q9q0qgmtz959rygieg9ln1l</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>77</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>77</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>77</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>R. Schmid</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.45888141</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>+0.07</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>77</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
         <v>3</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>N. Seiwald</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 6</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RCM(2)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>307whzq643o50rd4g8niobyay</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>97</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>97</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>RCM(2)</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>97</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>N. Seiwald</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.32985146</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>M. Gregoritsch</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7c6034wb3zsuq9nhxxiahiuol</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>84</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>84</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>84</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>M. Gregoritsch</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.14165779</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P. Wanner</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2yc1t7u26zctwjizi283g6q6s</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>67</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>67</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>67</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>P. Wanner</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.33945027</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>67</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>M. Sabitzer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>8cho2d1nz18i5o0zt6aysd68l</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>97</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>97</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>97</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>M. Sabitzer</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.77037245</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>+0.38</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M. Arnautović</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>dccxma9p13p00n0gi1cxk1nf9</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>67</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>30</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>97</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>M. Arnautović</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.006129130000000002</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C. Chukwuemeka</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 17</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5ql70wwevaoqpxabylew5f696</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>84</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>13</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>97</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>C. Chukwuemeka</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>-0.05714545999999998</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>84</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P. Wimmer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 21</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>aplc9mad75h1k90o3qla9c7l6</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>20</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>97</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>P. Wimmer</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.26134804</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>77</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A. Prass</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 22</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>33rjtcl9kkwdlp34oqn4dkx9m</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>67</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>97</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>30</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>A. Prass</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.01296044999999998</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>67</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6zhd6pt8kyzrbkgwq2i2k8u1g</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M. Friedl</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 23</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LCB(2)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>aaoycxwi9jny6flm4apz8a2uh</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>66</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>31</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>97</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>LCB(2)</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>31</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>61g4epojd5f198lv1sje27yh3</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>M. Friedl</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
+        <v>-0.05721294000000001</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
         <v>0</v>
       </c>
     </row>
